--- a/output/2026-10-11_08_Serbia_Sumadijski_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-11_08_Serbia_Sumadijski_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -474,7 +474,6 @@
           <t>Lazarević (punto vendita Messer Tehnogas)</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Cerovac, Kragujevac - Šumadijski</t>
@@ -490,7 +489,6 @@
           <t>034/6792-272</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Rivenditore locale di gas tecnici/industriali e attrezzature per saldatura e taglio (rete Messer Tehnogas), vende a officine/carpenterie/metalmeccanica. Categoria adiacente (gas tecnici/saldatura) non coincidente col core Dupuy (aspirazione/filtrazione/ATEX). Fonte: planplus.rs</t>
@@ -508,7 +506,6 @@
           <t>Tehnomont (punto vendita Messer Tehnogas)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Aranđelovac - Šumadijski</t>
@@ -524,7 +521,6 @@
           <t>034/6712-074</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Rivenditore/importatore locale gas tecnici e attrezzature saldatura/taglio (rete Messer Tehnogas). Categoria adiacente, non core Dupuy. Fonte: planplus.rs</t>
@@ -542,7 +538,6 @@
           <t>Sanu - sistemi za ventilaciju</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Kragujevac (Sušica) - Šumadijski</t>
@@ -558,10 +553,9 @@
           <t>062/148-7781</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Azienda in categoria impiantistica/sistemi di ventilazione, possibile overlap con aspirazione/depolverazione industriale. Ruolo di distributore vs installatore non pienamente confermato, richiede contatto diretto. Fonte: planplus.rs</t>
+          <t>Azienda in categoria impiantistica/sistemi di ventilazione, possibile overlap con aspirazione/depolverazione industriale. Ruolo di distributore vs installatore non pienamente confermato, richiede contatto diretto. Fonte: planplus.rs [DUPLICATO — vedi anche: 2026-10-11_05_Serbia_Sumadijski_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -576,7 +570,6 @@
           <t>Sloga d.o.o.</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Kragujevac - Šumadijski</t>
@@ -587,8 +580,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Rivenditore (Händler) di macchine usate per lavorazione metalli (deep-hole drilling: IXION, AUERBACH, IMSA, Technidrill, TBT), classificato come trader non come officina conto terzi. Nessun sito/telefono/email ufficiali reperiti. Fonte: machineseeker.rs</t>

--- a/output/2026-10-11_08_Serbia_Sumadijski_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-11_08_Serbia_Sumadijski_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
